--- a/Holdings09feb2026.xlsx
+++ b/Holdings09feb2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investment\October-Quaterly-Result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\Investment\pms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FFBE198-4590-4309-9CEB-6CCB58CE0339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCDF56C4-5018-4CC9-BE1F-5DCC0CD8B172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A59C9408-6FFB-4B1A-950F-E0ADD8156D3D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{A59C9408-6FFB-4B1A-950F-E0ADD8156D3D}"/>
   </bookViews>
   <sheets>
     <sheet name="Purchase Date Wise" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1021" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="425">
   <si>
     <t>ASIANPAINT</t>
   </si>
@@ -1448,6 +1448,24 @@
   </si>
   <si>
     <t>Hold</t>
+  </si>
+  <si>
+    <t>INE067A01029</t>
+  </si>
+  <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>ITC#</t>
+  </si>
+  <si>
+    <t>2026-02-04</t>
+  </si>
+  <si>
+    <t>2026-02-13</t>
+  </si>
+  <si>
+    <t>INE584A01023</t>
   </si>
 </sst>
 </file>
@@ -2090,7 +2108,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2190,6 +2208,10 @@
     <xf numFmtId="0" fontId="29" fillId="33" borderId="0" xfId="42" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="42" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2250,9 +2272,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2290,7 +2312,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2396,7 +2418,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2538,7 +2560,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5251,7 +5273,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFB35BFF-BF52-4112-B8CC-8F44E3B5BB33}">
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:T85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
@@ -6669,7 +6691,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A65" s="34" t="s">
         <v>266</v>
       </c>
@@ -6692,7 +6714,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A66" s="34" t="s">
         <v>6</v>
       </c>
@@ -6715,7 +6737,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A67" s="34" t="s">
         <v>32</v>
       </c>
@@ -6738,7 +6760,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A68" s="34" t="s">
         <v>307</v>
       </c>
@@ -6761,7 +6783,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="49" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:20" s="49" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="46" t="s">
         <v>290</v>
       </c>
@@ -6784,7 +6806,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A70" s="34" t="s">
         <v>0</v>
       </c>
@@ -6807,7 +6829,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A71" s="34" t="s">
         <v>29</v>
       </c>
@@ -6829,8 +6851,14 @@
       <c r="G71" s="37" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="O71" s="57"/>
+      <c r="P71" s="57"/>
+      <c r="Q71" s="57"/>
+      <c r="R71" s="58"/>
+      <c r="S71" s="58"/>
+      <c r="T71" s="58"/>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="34" t="s">
         <v>32</v>
       </c>
@@ -6849,9 +6877,17 @@
       <c r="F72" s="35">
         <v>220</v>
       </c>
-      <c r="G72" s="37"/>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G72" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="O72" s="57"/>
+      <c r="P72" s="57"/>
+      <c r="Q72" s="57"/>
+      <c r="R72" s="58"/>
+      <c r="S72" s="58"/>
+      <c r="T72" s="58"/>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="34" t="s">
         <v>32</v>
       </c>
@@ -6870,9 +6906,17 @@
       <c r="F73" s="35">
         <v>920</v>
       </c>
-      <c r="G73" s="37"/>
-    </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G73" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="O73" s="57"/>
+      <c r="P73" s="57"/>
+      <c r="Q73" s="57"/>
+      <c r="R73" s="58"/>
+      <c r="S73" s="58"/>
+      <c r="T73" s="58"/>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="34" t="s">
         <v>405</v>
       </c>
@@ -6891,9 +6935,17 @@
       <c r="F74" s="35">
         <v>120</v>
       </c>
-      <c r="G74" s="37"/>
-    </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="G74" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="O74" s="57"/>
+      <c r="P74" s="57"/>
+      <c r="Q74" s="57"/>
+      <c r="R74" s="58"/>
+      <c r="S74" s="58"/>
+      <c r="T74" s="58"/>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="34" t="s">
         <v>42</v>
       </c>
@@ -6912,111 +6964,181 @@
       <c r="F75" s="35">
         <v>240</v>
       </c>
-      <c r="G75" s="37"/>
-    </row>
-    <row r="76" spans="1:17" s="37" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="41" t="s">
-        <v>234</v>
-      </c>
-      <c r="B76" s="41" t="s">
-        <v>221</v>
-      </c>
-      <c r="C76" s="41" t="s">
-        <v>221</v>
-      </c>
-      <c r="D76" s="41" t="s">
-        <v>221</v>
-      </c>
-      <c r="E76" s="41" t="s">
-        <v>221</v>
-      </c>
-      <c r="F76" s="42">
-        <f>SUM(F45:F75)</f>
-        <v>15410.8</v>
+      <c r="G75" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="O75" s="57"/>
+      <c r="P75" s="57"/>
+      <c r="Q75" s="57"/>
+      <c r="R75" s="58"/>
+      <c r="S75" s="58"/>
+      <c r="T75" s="58"/>
+    </row>
+    <row r="76" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A76" s="57" t="s">
+        <v>154</v>
+      </c>
+      <c r="B76" s="57" t="s">
+        <v>419</v>
+      </c>
+      <c r="C76" s="57" t="s">
+        <v>420</v>
+      </c>
+      <c r="D76" s="58">
+        <v>50</v>
+      </c>
+      <c r="E76" s="58">
+        <v>1.3</v>
+      </c>
+      <c r="F76" s="58">
+        <v>65</v>
       </c>
       <c r="G76" s="37" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="L78" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="M78" s="34" t="s">
-        <v>296</v>
-      </c>
-      <c r="N78" s="34" t="s">
-        <v>404</v>
-      </c>
-      <c r="O78" s="35">
-        <v>20</v>
-      </c>
-      <c r="P78" s="35">
-        <v>11</v>
-      </c>
-      <c r="Q78" s="35">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="L79" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="M79" s="34" t="s">
-        <v>296</v>
-      </c>
-      <c r="N79" s="34" t="s">
-        <v>404</v>
-      </c>
-      <c r="O79" s="35">
-        <v>20</v>
-      </c>
-      <c r="P79" s="35">
-        <v>46</v>
-      </c>
-      <c r="Q79" s="35">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="L80" s="34" t="s">
-        <v>405</v>
-      </c>
-      <c r="M80" s="34" t="s">
-        <v>406</v>
-      </c>
-      <c r="N80" s="34" t="s">
-        <v>407</v>
-      </c>
-      <c r="O80" s="35">
-        <v>30</v>
-      </c>
-      <c r="P80" s="35">
-        <v>4</v>
-      </c>
-      <c r="Q80" s="35">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="81" spans="12:17" x14ac:dyDescent="0.25">
-      <c r="L81" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="M81" s="34" t="s">
-        <v>408</v>
-      </c>
-      <c r="N81" s="34" t="s">
-        <v>409</v>
-      </c>
-      <c r="O81" s="35">
-        <v>40</v>
-      </c>
-      <c r="P81" s="35">
-        <v>6</v>
-      </c>
-      <c r="Q81" s="35">
-        <v>240</v>
-      </c>
+      <c r="O76" s="57"/>
+      <c r="P76" s="57"/>
+      <c r="Q76" s="57"/>
+      <c r="R76" s="58"/>
+      <c r="S76" s="58"/>
+      <c r="T76" s="58"/>
+    </row>
+    <row r="77" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A77" s="57" t="s">
+        <v>421</v>
+      </c>
+      <c r="B77" s="57" t="s">
+        <v>248</v>
+      </c>
+      <c r="C77" s="57" t="s">
+        <v>422</v>
+      </c>
+      <c r="D77" s="58">
+        <v>300</v>
+      </c>
+      <c r="E77" s="58">
+        <v>6.5</v>
+      </c>
+      <c r="F77" s="58">
+        <v>1950</v>
+      </c>
+      <c r="G77" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="O77" s="57"/>
+      <c r="P77" s="57"/>
+      <c r="Q77" s="57"/>
+      <c r="R77" s="58"/>
+      <c r="S77" s="58"/>
+      <c r="T77" s="58"/>
+    </row>
+    <row r="78" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A78" s="57" t="s">
+        <v>29</v>
+      </c>
+      <c r="B78" s="57" t="s">
+        <v>262</v>
+      </c>
+      <c r="C78" s="57" t="s">
+        <v>423</v>
+      </c>
+      <c r="D78" s="58">
+        <v>50</v>
+      </c>
+      <c r="E78" s="58">
+        <v>1.25</v>
+      </c>
+      <c r="F78" s="58">
+        <v>62.5</v>
+      </c>
+      <c r="G78" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="O78" s="57"/>
+      <c r="P78" s="57"/>
+      <c r="Q78" s="57"/>
+      <c r="R78" s="58"/>
+      <c r="S78" s="58"/>
+      <c r="T78" s="58"/>
+    </row>
+    <row r="79" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A79" s="57" t="s">
+        <v>17</v>
+      </c>
+      <c r="B79" s="57" t="s">
+        <v>424</v>
+      </c>
+      <c r="C79" s="57" t="s">
+        <v>423</v>
+      </c>
+      <c r="D79" s="58">
+        <v>400</v>
+      </c>
+      <c r="E79" s="58">
+        <v>2.5</v>
+      </c>
+      <c r="F79" s="58">
+        <v>1000</v>
+      </c>
+      <c r="G79" s="37" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" s="37" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="41" t="s">
+        <v>234</v>
+      </c>
+      <c r="B80" s="41" t="s">
+        <v>221</v>
+      </c>
+      <c r="C80" s="41" t="s">
+        <v>221</v>
+      </c>
+      <c r="D80" s="41" t="s">
+        <v>221</v>
+      </c>
+      <c r="E80" s="41" t="s">
+        <v>221</v>
+      </c>
+      <c r="F80" s="42">
+        <f>SUM(F45:F79)</f>
+        <v>18488.3</v>
+      </c>
+      <c r="G80" s="37" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="82" spans="12:17" x14ac:dyDescent="0.25">
+      <c r="L82" s="34"/>
+      <c r="M82" s="34"/>
+      <c r="N82" s="34"/>
+      <c r="O82" s="35"/>
+      <c r="P82" s="35"/>
+      <c r="Q82" s="35"/>
+    </row>
+    <row r="83" spans="12:17" x14ac:dyDescent="0.25">
+      <c r="L83" s="34"/>
+      <c r="M83" s="34"/>
+      <c r="N83" s="34"/>
+      <c r="O83" s="35"/>
+      <c r="P83" s="35"/>
+      <c r="Q83" s="35"/>
+    </row>
+    <row r="84" spans="12:17" x14ac:dyDescent="0.25">
+      <c r="L84" s="34"/>
+      <c r="M84" s="34"/>
+      <c r="N84" s="34"/>
+      <c r="O84" s="35"/>
+      <c r="P84" s="35"/>
+      <c r="Q84" s="35"/>
+    </row>
+    <row r="85" spans="12:17" x14ac:dyDescent="0.25">
+      <c r="L85" s="34"/>
+      <c r="M85" s="34"/>
+      <c r="N85" s="34"/>
+      <c r="O85" s="35"/>
+      <c r="P85" s="35"/>
+      <c r="Q85" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="27" type="noConversion"/>

--- a/Holdings09feb2026.xlsx
+++ b/Holdings09feb2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\Investment\pms\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investment\pms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCDF56C4-5018-4CC9-BE1F-5DCC0CD8B172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7130A4-4545-4B36-AE37-FAA0501F61D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{A59C9408-6FFB-4B1A-950F-E0ADD8156D3D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{A59C9408-6FFB-4B1A-950F-E0ADD8156D3D}"/>
   </bookViews>
   <sheets>
     <sheet name="Purchase Date Wise" sheetId="6" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="426">
   <si>
     <t>ASIANPAINT</t>
   </si>
@@ -1466,6 +1466,9 @@
   </si>
   <si>
     <t>INE584A01023</t>
+  </si>
+  <si>
+    <t>SBI Liquid Fund</t>
   </si>
 </sst>
 </file>
@@ -2108,7 +2111,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2208,10 +2211,6 @@
     <xf numFmtId="0" fontId="29" fillId="33" borderId="0" xfId="42" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="42"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="42" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2272,9 +2271,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2312,7 +2311,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2418,7 +2417,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2560,7 +2559,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -6851,12 +6850,12 @@
       <c r="G71" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="O71" s="57"/>
-      <c r="P71" s="57"/>
-      <c r="Q71" s="57"/>
-      <c r="R71" s="58"/>
-      <c r="S71" s="58"/>
-      <c r="T71" s="58"/>
+      <c r="O71" s="34"/>
+      <c r="P71" s="34"/>
+      <c r="Q71" s="34"/>
+      <c r="R71" s="35"/>
+      <c r="S71" s="35"/>
+      <c r="T71" s="35"/>
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A72" s="34" t="s">
@@ -6880,12 +6879,12 @@
       <c r="G72" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="O72" s="57"/>
-      <c r="P72" s="57"/>
-      <c r="Q72" s="57"/>
-      <c r="R72" s="58"/>
-      <c r="S72" s="58"/>
-      <c r="T72" s="58"/>
+      <c r="O72" s="34"/>
+      <c r="P72" s="34"/>
+      <c r="Q72" s="34"/>
+      <c r="R72" s="35"/>
+      <c r="S72" s="35"/>
+      <c r="T72" s="35"/>
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A73" s="34" t="s">
@@ -6909,12 +6908,12 @@
       <c r="G73" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="O73" s="57"/>
-      <c r="P73" s="57"/>
-      <c r="Q73" s="57"/>
-      <c r="R73" s="58"/>
-      <c r="S73" s="58"/>
-      <c r="T73" s="58"/>
+      <c r="O73" s="34"/>
+      <c r="P73" s="34"/>
+      <c r="Q73" s="34"/>
+      <c r="R73" s="35"/>
+      <c r="S73" s="35"/>
+      <c r="T73" s="35"/>
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A74" s="34" t="s">
@@ -6938,12 +6937,12 @@
       <c r="G74" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="O74" s="57"/>
-      <c r="P74" s="57"/>
-      <c r="Q74" s="57"/>
-      <c r="R74" s="58"/>
-      <c r="S74" s="58"/>
-      <c r="T74" s="58"/>
+      <c r="O74" s="34"/>
+      <c r="P74" s="34"/>
+      <c r="Q74" s="34"/>
+      <c r="R74" s="35"/>
+      <c r="S74" s="35"/>
+      <c r="T74" s="35"/>
     </row>
     <row r="75" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A75" s="34" t="s">
@@ -6967,117 +6966,117 @@
       <c r="G75" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="O75" s="57"/>
-      <c r="P75" s="57"/>
-      <c r="Q75" s="57"/>
-      <c r="R75" s="58"/>
-      <c r="S75" s="58"/>
-      <c r="T75" s="58"/>
+      <c r="O75" s="34"/>
+      <c r="P75" s="34"/>
+      <c r="Q75" s="34"/>
+      <c r="R75" s="35"/>
+      <c r="S75" s="35"/>
+      <c r="T75" s="35"/>
     </row>
     <row r="76" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A76" s="57" t="s">
+      <c r="A76" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="B76" s="57" t="s">
+      <c r="B76" s="34" t="s">
         <v>419</v>
       </c>
-      <c r="C76" s="57" t="s">
+      <c r="C76" s="34" t="s">
         <v>420</v>
       </c>
-      <c r="D76" s="58">
+      <c r="D76" s="35">
         <v>50</v>
       </c>
-      <c r="E76" s="58">
+      <c r="E76" s="35">
         <v>1.3</v>
       </c>
-      <c r="F76" s="58">
+      <c r="F76" s="35">
         <v>65</v>
       </c>
       <c r="G76" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="O76" s="57"/>
-      <c r="P76" s="57"/>
-      <c r="Q76" s="57"/>
-      <c r="R76" s="58"/>
-      <c r="S76" s="58"/>
-      <c r="T76" s="58"/>
+      <c r="O76" s="34"/>
+      <c r="P76" s="34"/>
+      <c r="Q76" s="34"/>
+      <c r="R76" s="35"/>
+      <c r="S76" s="35"/>
+      <c r="T76" s="35"/>
     </row>
     <row r="77" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A77" s="57" t="s">
+      <c r="A77" s="34" t="s">
         <v>421</v>
       </c>
-      <c r="B77" s="57" t="s">
+      <c r="B77" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="C77" s="57" t="s">
+      <c r="C77" s="34" t="s">
         <v>422</v>
       </c>
-      <c r="D77" s="58">
+      <c r="D77" s="35">
         <v>300</v>
       </c>
-      <c r="E77" s="58">
+      <c r="E77" s="35">
         <v>6.5</v>
       </c>
-      <c r="F77" s="58">
+      <c r="F77" s="35">
         <v>1950</v>
       </c>
       <c r="G77" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="O77" s="57"/>
-      <c r="P77" s="57"/>
-      <c r="Q77" s="57"/>
-      <c r="R77" s="58"/>
-      <c r="S77" s="58"/>
-      <c r="T77" s="58"/>
+      <c r="O77" s="34"/>
+      <c r="P77" s="34"/>
+      <c r="Q77" s="34"/>
+      <c r="R77" s="35"/>
+      <c r="S77" s="35"/>
+      <c r="T77" s="35"/>
     </row>
     <row r="78" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A78" s="57" t="s">
+      <c r="A78" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="B78" s="57" t="s">
+      <c r="B78" s="34" t="s">
         <v>262</v>
       </c>
-      <c r="C78" s="57" t="s">
+      <c r="C78" s="34" t="s">
         <v>423</v>
       </c>
-      <c r="D78" s="58">
+      <c r="D78" s="35">
         <v>50</v>
       </c>
-      <c r="E78" s="58">
+      <c r="E78" s="35">
         <v>1.25</v>
       </c>
-      <c r="F78" s="58">
+      <c r="F78" s="35">
         <v>62.5</v>
       </c>
       <c r="G78" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="O78" s="57"/>
-      <c r="P78" s="57"/>
-      <c r="Q78" s="57"/>
-      <c r="R78" s="58"/>
-      <c r="S78" s="58"/>
-      <c r="T78" s="58"/>
+      <c r="O78" s="34"/>
+      <c r="P78" s="34"/>
+      <c r="Q78" s="34"/>
+      <c r="R78" s="35"/>
+      <c r="S78" s="35"/>
+      <c r="T78" s="35"/>
     </row>
     <row r="79" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A79" s="57" t="s">
+      <c r="A79" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B79" s="57" t="s">
+      <c r="B79" s="34" t="s">
         <v>424</v>
       </c>
-      <c r="C79" s="57" t="s">
+      <c r="C79" s="34" t="s">
         <v>423</v>
       </c>
-      <c r="D79" s="58">
+      <c r="D79" s="35">
         <v>400</v>
       </c>
-      <c r="E79" s="58">
+      <c r="E79" s="35">
         <v>2.5</v>
       </c>
-      <c r="F79" s="58">
+      <c r="F79" s="35">
         <v>1000</v>
       </c>
       <c r="G79" s="37" t="s">
@@ -9932,7 +9931,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF0D7A38-777D-459A-9871-9DE810D259DB}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57.28515625" bestFit="1" customWidth="1"/>
@@ -9963,264 +9962,260 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="B2" s="20">
-        <v>127.94</v>
-      </c>
-      <c r="C2" s="20">
-        <v>121.64</v>
-      </c>
-      <c r="D2" s="21">
-        <v>8.5000000000000006E-3</v>
-      </c>
-      <c r="E2" s="20">
+    <row r="2" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="23">
+        <v>20.07</v>
+      </c>
+      <c r="C2" s="23">
+        <v>19.48</v>
+      </c>
+      <c r="D2" s="24">
+        <v>2.7000000000000001E-3</v>
+      </c>
+      <c r="E2" s="25">
         <f>(B2-C2)</f>
-        <v>6.2999999999999972</v>
-      </c>
-      <c r="F2" s="22">
+        <v>0.58999999999999986</v>
+      </c>
+      <c r="F2" s="26">
         <f>ROUNDUP(E2/(B2/100),2)</f>
-        <v>4.93</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B3">
-        <v>910.66</v>
+        <v>226.08</v>
       </c>
       <c r="C3">
-        <v>893.11</v>
+        <v>223.89</v>
       </c>
       <c r="D3" s="21">
-        <v>6.7000000000000002E-3</v>
+        <v>7.4999999999999997E-3</v>
       </c>
       <c r="E3" s="20">
-        <f t="shared" ref="E3:E35" si="0">(B3-C3)</f>
-        <v>17.549999999999955</v>
+        <f>(B3-C3)</f>
+        <v>2.1900000000000261</v>
       </c>
       <c r="F3" s="22">
-        <f t="shared" ref="F3:F35" si="1">ROUNDUP(E3/(B3/100),2)</f>
-        <v>1.93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B4">
-        <v>20.41</v>
-      </c>
-      <c r="C4">
-        <v>20.41</v>
-      </c>
-      <c r="D4" s="21">
-        <v>6.1000000000000004E-3</v>
-      </c>
-      <c r="E4" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F4" s="22">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>ROUNDUP(E3/(B3/100),2)</f>
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="23">
+        <v>20.28</v>
+      </c>
+      <c r="C4" s="23">
+        <v>18.97</v>
+      </c>
+      <c r="D4" s="24">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E4" s="25">
+        <f>(B4-C4)</f>
+        <v>1.3100000000000023</v>
+      </c>
+      <c r="F4" s="26">
+        <f>ROUNDUP(E4/(B4/100),2)</f>
+        <v>6.46</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5">
+        <v>18.09</v>
+      </c>
+      <c r="C5">
+        <v>19.71</v>
+      </c>
+      <c r="D5" s="21">
+        <v>9.1999999999999998E-3</v>
+      </c>
+      <c r="E5" s="20">
+        <f>(B5-C5)</f>
+        <v>-1.620000000000001</v>
+      </c>
+      <c r="F5" s="22">
+        <f>ROUNDUP(E5/(B5/100),2)</f>
+        <v>-8.9599999999999991</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>119</v>
       </c>
-      <c r="B5">
+      <c r="B6">
         <v>36.08</v>
       </c>
-      <c r="C5">
-        <v>34.67</v>
-      </c>
-      <c r="D5" s="21">
+      <c r="C6">
+        <v>35.01</v>
+      </c>
+      <c r="D6" s="21">
         <v>9.7999999999999997E-3</v>
       </c>
-      <c r="E5" s="20">
-        <f t="shared" si="0"/>
-        <v>1.4099999999999966</v>
-      </c>
-      <c r="F5" s="22">
-        <f t="shared" si="1"/>
-        <v>3.9099999999999997</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="B6" s="23">
-        <v>20.28</v>
-      </c>
-      <c r="C6" s="23">
-        <v>16.68</v>
-      </c>
-      <c r="D6" s="24">
-        <v>3.0000000000000001E-3</v>
-      </c>
-      <c r="E6" s="25">
-        <f t="shared" si="0"/>
-        <v>3.6000000000000014</v>
-      </c>
-      <c r="F6" s="26">
-        <f t="shared" si="1"/>
-        <v>17.760000000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>121</v>
-      </c>
-      <c r="B7">
-        <v>226.08</v>
-      </c>
-      <c r="C7">
-        <v>217.29</v>
+      <c r="E6" s="20">
+        <f>(B6-C6)</f>
+        <v>1.0700000000000003</v>
+      </c>
+      <c r="F6" s="22">
+        <f>ROUNDUP(E6/(B6/100),2)</f>
+        <v>2.9699999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7" s="20">
+        <v>128.4</v>
+      </c>
+      <c r="C7" s="20">
+        <v>119.11</v>
       </c>
       <c r="D7" s="21">
-        <v>7.4999999999999997E-3</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="E7" s="20">
-        <f t="shared" si="0"/>
-        <v>8.7900000000000205</v>
+        <f>(B7-C7)</f>
+        <v>9.2900000000000063</v>
       </c>
       <c r="F7" s="22">
-        <f t="shared" si="1"/>
-        <v>3.8899999999999997</v>
+        <f>ROUNDUP(E7/(B7/100),2)</f>
+        <v>7.24</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B8">
-        <v>18.09</v>
+        <v>910.66</v>
       </c>
       <c r="C8">
-        <v>16.86</v>
+        <v>897.34</v>
       </c>
       <c r="D8" s="21">
-        <v>9.1999999999999998E-3</v>
+        <v>6.7000000000000002E-3</v>
       </c>
       <c r="E8" s="20">
-        <f t="shared" si="0"/>
-        <v>1.2300000000000004</v>
+        <f t="shared" ref="E8:E42" si="0">(B8-C8)</f>
+        <v>13.319999999999936</v>
       </c>
       <c r="F8" s="22">
-        <f t="shared" si="1"/>
-        <v>6.8</v>
+        <f t="shared" ref="F8:F42" si="1">ROUNDUP(E8/(B8/100),2)</f>
+        <v>1.47</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B9">
-        <v>9.92</v>
+        <v>20.41</v>
       </c>
       <c r="C9">
-        <v>9.42</v>
-      </c>
-      <c r="D9" s="21"/>
+        <v>23.55</v>
+      </c>
+      <c r="D9" s="21">
+        <v>6.1000000000000004E-3</v>
+      </c>
       <c r="E9" s="20">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>-3.1400000000000006</v>
       </c>
       <c r="F9" s="22">
         <f t="shared" si="1"/>
-        <v>5.05</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
+        <v>-15.39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B10" s="23">
-        <v>243.78</v>
+        <v>44.37</v>
       </c>
       <c r="C10" s="23">
-        <v>232.73</v>
-      </c>
-      <c r="D10" s="24">
-        <v>1.9E-3</v>
-      </c>
-      <c r="E10" s="25">
-        <f t="shared" si="0"/>
-        <v>11.050000000000011</v>
-      </c>
-      <c r="F10" s="19">
-        <f t="shared" si="1"/>
-        <v>4.54</v>
+        <v>45.01</v>
+      </c>
+      <c r="D10" s="27"/>
+      <c r="E10" s="20">
+        <f>(B10-C10)</f>
+        <v>-0.64000000000000057</v>
+      </c>
+      <c r="F10" s="22">
+        <f>ROUNDUP(E10/(B10/100),2)</f>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B11" s="23">
-        <v>10.84</v>
+        <v>19.25</v>
       </c>
       <c r="C11" s="23">
-        <v>8.73</v>
-      </c>
-      <c r="D11" s="24">
-        <v>4.7000000000000002E-3</v>
-      </c>
+        <v>17.53</v>
+      </c>
+      <c r="D11" s="24"/>
       <c r="E11" s="25">
-        <f t="shared" si="0"/>
-        <v>2.1099999999999994</v>
-      </c>
-      <c r="F11" s="19">
-        <f t="shared" si="1"/>
-        <v>19.470000000000002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
+        <f>(B11-C11)</f>
+        <v>1.7199999999999989</v>
+      </c>
+      <c r="F11" s="26">
+        <f>ROUNDUP(E11/(B11/100),2)</f>
+        <v>8.94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="23" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="B12" s="23">
-        <v>19.25</v>
+        <v>407.44</v>
       </c>
       <c r="C12" s="23">
-        <v>16.36</v>
-      </c>
-      <c r="D12" s="24"/>
-      <c r="E12" s="25">
-        <f t="shared" si="0"/>
-        <v>2.8900000000000006</v>
+        <v>422.52</v>
+      </c>
+      <c r="D12" s="27"/>
+      <c r="E12" s="20">
+        <f>(B12-C12)</f>
+        <v>-15.079999999999984</v>
       </c>
       <c r="F12" s="26">
-        <f t="shared" si="1"/>
-        <v>15.02</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
+        <f>ROUNDUP(E12/(B12/100),2)</f>
+        <v>-3.71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="23" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B13" s="23">
-        <v>20.07</v>
+        <v>51.04</v>
       </c>
       <c r="C13" s="23">
-        <v>16.96</v>
-      </c>
-      <c r="D13" s="24">
-        <v>2.7000000000000001E-3</v>
-      </c>
-      <c r="E13" s="25">
-        <f t="shared" si="0"/>
-        <v>3.1099999999999994</v>
-      </c>
-      <c r="F13" s="26">
-        <f t="shared" si="1"/>
-        <v>15.5</v>
+        <v>49.04</v>
+      </c>
+      <c r="D13" s="27"/>
+      <c r="E13" s="20">
+        <f>(B13-C13)</f>
+        <v>2</v>
+      </c>
+      <c r="F13" s="22">
+        <f>ROUNDUP(E13/(B13/100),2)</f>
+        <v>3.92</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -10231,378 +10226,392 @@
         <v>402.46</v>
       </c>
       <c r="C14" s="23">
-        <v>331.35</v>
+        <v>337.14</v>
       </c>
       <c r="D14" s="27"/>
       <c r="E14" s="20">
-        <f t="shared" si="0"/>
-        <v>71.109999999999957</v>
+        <f>(B14-C14)</f>
+        <v>65.319999999999993</v>
       </c>
       <c r="F14" s="26">
-        <f t="shared" si="1"/>
-        <v>17.670000000000002</v>
+        <f>ROUNDUP(E14/(B14/100),2)</f>
+        <v>16.240000000000002</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="B15" s="23">
-        <v>51.04</v>
-      </c>
-      <c r="C15" s="23">
-        <v>50.32</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
       <c r="D15" s="27"/>
-      <c r="E15" s="20">
-        <f t="shared" si="0"/>
-        <v>0.71999999999999886</v>
-      </c>
-      <c r="F15" s="22">
-        <f t="shared" si="1"/>
-        <v>1.42</v>
-      </c>
+      <c r="E15" s="20"/>
+      <c r="F15" s="22"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="B16" s="23">
-        <v>44.37</v>
-      </c>
-      <c r="C16" s="23">
-        <v>40.479999999999997</v>
-      </c>
-      <c r="D16" s="27"/>
+      <c r="A16" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16">
+        <v>9.92</v>
+      </c>
+      <c r="C16">
+        <v>9.6</v>
+      </c>
+      <c r="D16" s="21"/>
       <c r="E16" s="20">
         <f t="shared" si="0"/>
-        <v>3.8900000000000006</v>
+        <v>0.32000000000000028</v>
       </c>
       <c r="F16" s="22">
         <f t="shared" si="1"/>
-        <v>8.77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+        <v>3.23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" s="23" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="23" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B17" s="23">
-        <v>407.44</v>
+        <v>243.78</v>
       </c>
       <c r="C17" s="23">
-        <v>349.52</v>
-      </c>
-      <c r="D17" s="27"/>
-      <c r="E17" s="20">
+        <v>224.62</v>
+      </c>
+      <c r="D17" s="24">
+        <v>1.9E-3</v>
+      </c>
+      <c r="E17" s="25">
         <f t="shared" si="0"/>
-        <v>57.920000000000016</v>
-      </c>
-      <c r="F17" s="26">
+        <v>19.159999999999997</v>
+      </c>
+      <c r="F17" s="19">
         <f t="shared" si="1"/>
-        <v>14.22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D18" s="27"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="22"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="23" t="s">
+        <v>7.8599999999999994</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" s="23" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="B18" s="23">
+        <v>10.84</v>
+      </c>
+      <c r="C18" s="23">
+        <v>8.68</v>
+      </c>
+      <c r="D18" s="24">
+        <v>4.7000000000000002E-3</v>
+      </c>
+      <c r="E18" s="25">
+        <f t="shared" si="0"/>
+        <v>2.16</v>
+      </c>
+      <c r="F18" s="19">
+        <f t="shared" si="1"/>
+        <v>19.930000000000003</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D25" s="27"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="22"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B26" s="23">
         <v>187</v>
       </c>
-      <c r="C19" s="23">
+      <c r="C26" s="23">
         <v>138.91999999999999</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E26" s="25">
         <f t="shared" si="0"/>
         <v>48.080000000000013</v>
       </c>
-      <c r="F19" s="28">
+      <c r="F26" s="28">
         <f t="shared" si="1"/>
         <v>25.720000000000002</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="23" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="23">
+      <c r="B27" s="23">
         <v>180</v>
       </c>
-      <c r="C20" s="23">
+      <c r="C27" s="23">
         <v>139.94</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E27" s="25">
         <f t="shared" si="0"/>
         <v>40.06</v>
       </c>
-      <c r="F20" s="28">
+      <c r="F27" s="28">
         <f t="shared" si="1"/>
         <v>22.26</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="23" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B28" s="23">
         <v>180</v>
       </c>
-      <c r="C21" s="23">
+      <c r="C28" s="23">
         <v>138.75</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E28" s="25">
         <f t="shared" si="0"/>
         <v>41.25</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F28" s="28">
         <f t="shared" si="1"/>
         <v>22.92</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="23" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="B22" s="23">
+      <c r="B29" s="23">
         <v>194.8</v>
       </c>
-      <c r="C22" s="23">
+      <c r="C29" s="23">
         <v>142.24</v>
       </c>
-      <c r="E22" s="25">
+      <c r="E29" s="25">
         <f t="shared" si="0"/>
         <v>52.56</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F29" s="19">
         <f t="shared" si="1"/>
         <v>26.990000000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="23"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="19"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="23" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="23"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="19"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="23" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="23">
+      <c r="B31" s="23">
         <v>139</v>
       </c>
-      <c r="C24" s="23">
+      <c r="C31" s="23">
         <v>132.41999999999999</v>
       </c>
-      <c r="E24" s="25">
+      <c r="E31" s="25">
         <f t="shared" si="0"/>
         <v>6.5800000000000125</v>
       </c>
-      <c r="F24" s="19">
+      <c r="F31" s="19">
         <f t="shared" si="1"/>
         <v>4.74</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="23" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="23">
+      <c r="B32" s="23">
         <v>135.9</v>
       </c>
-      <c r="C25" s="23">
+      <c r="C32" s="23">
         <v>127.42</v>
       </c>
-      <c r="E25" s="25">
+      <c r="E32" s="25">
         <f t="shared" si="0"/>
         <v>8.480000000000004</v>
       </c>
-      <c r="F25" s="19">
+      <c r="F32" s="19">
         <f t="shared" si="1"/>
         <v>6.24</v>
       </c>
     </row>
-    <row r="26" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="29" t="s">
+    <row r="33" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="B26" s="29">
+      <c r="B33" s="29">
         <v>142.22</v>
       </c>
-      <c r="C26" s="29">
+      <c r="C33" s="29">
         <v>131.51</v>
       </c>
-      <c r="E26" s="29">
+      <c r="E33" s="29">
         <f t="shared" si="0"/>
         <v>10.710000000000008</v>
       </c>
-      <c r="F26" s="28">
+      <c r="F33" s="28">
         <f t="shared" si="1"/>
         <v>7.54</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="23" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="B27" s="31">
+      <c r="B34" s="31">
         <v>11477</v>
       </c>
-      <c r="C27" s="23">
+      <c r="C34" s="23">
         <v>10194.200000000001</v>
       </c>
-      <c r="E27" s="25">
+      <c r="E34" s="25">
         <f t="shared" si="0"/>
         <v>1282.7999999999993</v>
       </c>
-      <c r="F27" s="19">
+      <c r="F34" s="19">
         <f t="shared" si="1"/>
         <v>11.18</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="23" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="B28" s="23">
+      <c r="B35" s="23">
         <v>93</v>
       </c>
-      <c r="C28" s="23">
+      <c r="C35" s="23">
         <v>91.29</v>
       </c>
-      <c r="E28" s="25">
+      <c r="E35" s="25">
         <f t="shared" si="0"/>
         <v>1.7099999999999937</v>
       </c>
-      <c r="F28" s="19">
+      <c r="F35" s="19">
         <f t="shared" si="1"/>
         <v>1.84</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="23" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="B29" s="23">
+      <c r="B36" s="23">
         <v>109.9</v>
       </c>
-      <c r="C29" s="23">
+      <c r="C36" s="23">
         <v>108.05</v>
       </c>
-      <c r="E29" s="25">
+      <c r="E36" s="25">
         <f t="shared" si="0"/>
         <v>1.8500000000000085</v>
       </c>
-      <c r="F29" s="19">
+      <c r="F36" s="19">
         <f t="shared" si="1"/>
         <v>1.69</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="23" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="B30" s="23">
+      <c r="B37" s="23">
         <v>96.96</v>
       </c>
-      <c r="C30" s="23">
+      <c r="C37" s="23">
         <v>94.19</v>
       </c>
-      <c r="E30" s="25">
+      <c r="E37" s="25">
         <f t="shared" si="0"/>
         <v>2.769999999999996</v>
       </c>
-      <c r="F30" s="19">
+      <c r="F37" s="19">
         <f t="shared" si="1"/>
         <v>2.86</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="23" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="B31" s="23">
+      <c r="B38" s="23">
         <v>17.920000000000002</v>
       </c>
-      <c r="C31" s="23">
+      <c r="C38" s="23">
         <v>17.329999999999998</v>
       </c>
-      <c r="E31" s="25">
+      <c r="E38" s="25">
         <f t="shared" si="0"/>
         <v>0.59000000000000341</v>
       </c>
-      <c r="F31" s="19">
+      <c r="F38" s="19">
         <f t="shared" si="1"/>
         <v>3.3</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E32" s="25"/>
-      <c r="F32" s="19"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="23" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E39" s="25"/>
+      <c r="F39" s="19"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="B33" s="23">
+      <c r="B40" s="23">
         <v>81.62</v>
       </c>
-      <c r="C33" s="23">
+      <c r="C40" s="23">
         <v>71.62</v>
       </c>
-      <c r="D33">
+      <c r="D40">
         <v>0.1</v>
       </c>
-      <c r="E33" s="25">
+      <c r="E40" s="25">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="F33" s="19">
+      <c r="F40" s="19">
         <f t="shared" si="1"/>
         <v>12.26</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="23" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="B34" s="23">
+      <c r="B41" s="23">
         <v>825.6</v>
       </c>
-      <c r="C34" s="23">
+      <c r="C41" s="23">
         <v>738.76</v>
       </c>
-      <c r="E34" s="25">
+      <c r="E41" s="25">
         <f t="shared" si="0"/>
         <v>86.840000000000032</v>
       </c>
-      <c r="F34" s="19">
+      <c r="F41" s="19">
         <f t="shared" si="1"/>
         <v>10.52</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="23" t="s">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="B35" s="23">
+      <c r="B42" s="23">
         <v>189.95</v>
       </c>
-      <c r="C35" s="23">
+      <c r="C42" s="23">
         <v>172.88</v>
       </c>
-      <c r="E35" s="25">
+      <c r="E42" s="25">
         <f t="shared" si="0"/>
         <v>17.069999999999993</v>
       </c>
-      <c r="F35" s="19">
+      <c r="F42" s="19">
         <f t="shared" si="1"/>
         <v>8.99</v>
       </c>

--- a/Holdings09feb2026.xlsx
+++ b/Holdings09feb2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investment\pms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7130A4-4545-4B36-AE37-FAA0501F61D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2B4786-C549-4518-B601-F583EBFE6E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{A59C9408-6FFB-4B1A-950F-E0ADD8156D3D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{A59C9408-6FFB-4B1A-950F-E0ADD8156D3D}"/>
   </bookViews>
   <sheets>
     <sheet name="Purchase Date Wise" sheetId="6" r:id="rId1"/>
@@ -28,22 +28,11 @@
     <sheet name="Sheet2" sheetId="17" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="426">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="442">
   <si>
     <t>ASIANPAINT</t>
   </si>
@@ -1469,6 +1458,54 @@
   </si>
   <si>
     <t>SBI Liquid Fund</t>
+  </si>
+  <si>
+    <t>2026-2027</t>
+  </si>
+  <si>
+    <t>INE200M01039</t>
+  </si>
+  <si>
+    <t>2026-04-08</t>
+  </si>
+  <si>
+    <t>2026-04-30</t>
+  </si>
+  <si>
+    <t>2026-05-15</t>
+  </si>
+  <si>
+    <t>INE379A01028</t>
+  </si>
+  <si>
+    <t>2026-05-21</t>
+  </si>
+  <si>
+    <t>2026-05-22</t>
+  </si>
+  <si>
+    <t>2026-05-25</t>
+  </si>
+  <si>
+    <t>2026-05-27</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>INE202B01038</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2026-06-19</t>
+  </si>
+  <si>
+    <t>2026-06-23</t>
+  </si>
+  <si>
+    <t>SAMVARDHANA</t>
   </si>
 </sst>
 </file>
@@ -2111,7 +2148,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2211,6 +2248,14 @@
     <xf numFmtId="0" fontId="29" fillId="33" borderId="0" xfId="42" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="42"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="42" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="42" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -5272,7 +5317,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFB35BFF-BF52-4112-B8CC-8F44E3B5BB33}">
-  <dimension ref="A1:T85"/>
+  <dimension ref="A1:T98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
@@ -7107,7 +7152,22 @@
         <v>312</v>
       </c>
     </row>
-    <row r="82" spans="12:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>441</v>
+      </c>
+      <c r="C82" s="60">
+        <v>46125</v>
+      </c>
+      <c r="D82" s="59">
+        <v>300</v>
+      </c>
+      <c r="F82" s="59">
+        <v>105</v>
+      </c>
+      <c r="G82" s="37" t="s">
+        <v>426</v>
+      </c>
       <c r="L82" s="34"/>
       <c r="M82" s="34"/>
       <c r="N82" s="34"/>
@@ -7115,7 +7175,28 @@
       <c r="P82" s="35"/>
       <c r="Q82" s="35"/>
     </row>
-    <row r="83" spans="12:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B83" s="46" t="s">
+        <v>427</v>
+      </c>
+      <c r="C83" s="46" t="s">
+        <v>428</v>
+      </c>
+      <c r="D83" s="47">
+        <v>100</v>
+      </c>
+      <c r="E83" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="F83" s="47">
+        <v>50</v>
+      </c>
+      <c r="G83" s="37" t="s">
+        <v>426</v>
+      </c>
       <c r="L83" s="34"/>
       <c r="M83" s="34"/>
       <c r="N83" s="34"/>
@@ -7123,7 +7204,25 @@
       <c r="P83" s="35"/>
       <c r="Q83" s="35"/>
     </row>
-    <row r="84" spans="12:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="B84" s="46" t="s">
+        <v>427</v>
+      </c>
+      <c r="C84" s="46" t="s">
+        <v>429</v>
+      </c>
+      <c r="D84" s="47">
+        <v>100</v>
+      </c>
+      <c r="E84" s="47">
+        <v>0.5</v>
+      </c>
+      <c r="F84" s="47">
+        <v>50</v>
+      </c>
       <c r="L84" s="34"/>
       <c r="M84" s="34"/>
       <c r="N84" s="34"/>
@@ -7131,13 +7230,291 @@
       <c r="P84" s="35"/>
       <c r="Q84" s="35"/>
     </row>
-    <row r="85" spans="12:17" x14ac:dyDescent="0.25">
-      <c r="L85" s="34"/>
-      <c r="M85" s="34"/>
-      <c r="N85" s="34"/>
-      <c r="O85" s="35"/>
-      <c r="P85" s="35"/>
-      <c r="Q85" s="35"/>
+    <row r="85" spans="1:17" s="49" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="46" t="s">
+        <v>277</v>
+      </c>
+      <c r="B85" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="C85" s="46" t="s">
+        <v>430</v>
+      </c>
+      <c r="D85" s="47">
+        <v>100</v>
+      </c>
+      <c r="E85" s="47">
+        <v>17.350000000000001</v>
+      </c>
+      <c r="F85" s="47">
+        <v>1735</v>
+      </c>
+      <c r="L85" s="46"/>
+      <c r="M85" s="46"/>
+      <c r="N85" s="46"/>
+      <c r="O85" s="47"/>
+      <c r="P85" s="47"/>
+      <c r="Q85" s="47"/>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86" s="57" t="s">
+        <v>431</v>
+      </c>
+      <c r="C86" s="57" t="s">
+        <v>432</v>
+      </c>
+      <c r="D86" s="58">
+        <v>20</v>
+      </c>
+      <c r="E86" s="58">
+        <v>1</v>
+      </c>
+      <c r="F86" s="58">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" s="49" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="46" t="s">
+        <v>405</v>
+      </c>
+      <c r="B87" s="46" t="s">
+        <v>406</v>
+      </c>
+      <c r="C87" s="46" t="s">
+        <v>433</v>
+      </c>
+      <c r="D87" s="47">
+        <v>50</v>
+      </c>
+      <c r="E87" s="47">
+        <v>6</v>
+      </c>
+      <c r="F87" s="47">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" s="49" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="B88" s="46" t="s">
+        <v>296</v>
+      </c>
+      <c r="C88" s="46" t="s">
+        <v>434</v>
+      </c>
+      <c r="D88" s="47">
+        <v>20</v>
+      </c>
+      <c r="E88" s="47">
+        <v>31</v>
+      </c>
+      <c r="F88" s="47">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89" s="57" t="s">
+        <v>421</v>
+      </c>
+      <c r="B89" s="57" t="s">
+        <v>248</v>
+      </c>
+      <c r="C89" s="57" t="s">
+        <v>435</v>
+      </c>
+      <c r="D89" s="58">
+        <v>400</v>
+      </c>
+      <c r="E89" s="58">
+        <v>8</v>
+      </c>
+      <c r="F89" s="58">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" s="49" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="B90" s="46" t="s">
+        <v>190</v>
+      </c>
+      <c r="C90" s="46" t="s">
+        <v>436</v>
+      </c>
+      <c r="D90" s="47">
+        <v>30</v>
+      </c>
+      <c r="E90" s="47">
+        <v>25</v>
+      </c>
+      <c r="F90" s="47">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91" s="57" t="s">
+        <v>152</v>
+      </c>
+      <c r="B91" s="57" t="s">
+        <v>437</v>
+      </c>
+      <c r="C91" s="57" t="s">
+        <v>438</v>
+      </c>
+      <c r="D91" s="58">
+        <v>5</v>
+      </c>
+      <c r="E91" s="58">
+        <v>11</v>
+      </c>
+      <c r="F91" s="58">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92" s="57" t="s">
+        <v>35</v>
+      </c>
+      <c r="B92" s="57" t="s">
+        <v>287</v>
+      </c>
+      <c r="C92" s="57" t="s">
+        <v>438</v>
+      </c>
+      <c r="D92" s="58">
+        <v>60</v>
+      </c>
+      <c r="E92" s="58">
+        <v>4</v>
+      </c>
+      <c r="F92" s="58">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" s="49" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B93" s="46" t="s">
+        <v>285</v>
+      </c>
+      <c r="C93" s="46" t="s">
+        <v>438</v>
+      </c>
+      <c r="D93" s="47">
+        <v>775</v>
+      </c>
+      <c r="E93" s="47">
+        <v>3</v>
+      </c>
+      <c r="F93" s="47">
+        <v>2325</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94" s="57" t="s">
+        <v>8</v>
+      </c>
+      <c r="B94" s="57" t="s">
+        <v>289</v>
+      </c>
+      <c r="C94" s="57" t="s">
+        <v>439</v>
+      </c>
+      <c r="D94" s="58">
+        <v>110</v>
+      </c>
+      <c r="E94" s="58">
+        <v>2.1</v>
+      </c>
+      <c r="F94" s="58">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A95" s="57" t="s">
+        <v>183</v>
+      </c>
+      <c r="B95" s="57" t="s">
+        <v>184</v>
+      </c>
+      <c r="C95" s="57" t="s">
+        <v>439</v>
+      </c>
+      <c r="D95" s="58">
+        <v>30</v>
+      </c>
+      <c r="E95" s="58">
+        <v>13</v>
+      </c>
+      <c r="F95" s="58">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A96" s="57" t="s">
+        <v>0</v>
+      </c>
+      <c r="B96" s="57" t="s">
+        <v>272</v>
+      </c>
+      <c r="C96" s="57" t="s">
+        <v>440</v>
+      </c>
+      <c r="D96" s="58">
+        <v>20</v>
+      </c>
+      <c r="E96" s="58">
+        <v>23</v>
+      </c>
+      <c r="F96" s="58">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="57" t="s">
+        <v>30</v>
+      </c>
+      <c r="B97" s="57" t="s">
+        <v>288</v>
+      </c>
+      <c r="C97" s="57" t="s">
+        <v>440</v>
+      </c>
+      <c r="D97" s="58">
+        <v>125</v>
+      </c>
+      <c r="E97" s="58">
+        <v>2.5</v>
+      </c>
+      <c r="F97" s="58">
+        <v>312.5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="57" t="s">
+        <v>290</v>
+      </c>
+      <c r="B98" s="57" t="s">
+        <v>189</v>
+      </c>
+      <c r="C98" s="57" t="s">
+        <v>440</v>
+      </c>
+      <c r="D98" s="58">
+        <v>90</v>
+      </c>
+      <c r="E98" s="58">
+        <v>22</v>
+      </c>
+      <c r="F98" s="58">
+        <v>1980</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="27" type="noConversion"/>
@@ -9970,18 +10347,18 @@
         <v>20.07</v>
       </c>
       <c r="C2" s="23">
-        <v>19.48</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="D2" s="24">
         <v>2.7000000000000001E-3</v>
       </c>
       <c r="E2" s="25">
-        <f>(B2-C2)</f>
-        <v>0.58999999999999986</v>
+        <f t="shared" ref="E2:E7" si="0">(B2-C2)</f>
+        <v>1.0599999999999987</v>
       </c>
       <c r="F2" s="26">
-        <f>ROUNDUP(E2/(B2/100),2)</f>
-        <v>2.94</v>
+        <f t="shared" ref="F2:F7" si="1">ROUNDUP(E2/(B2/100),2)</f>
+        <v>5.29</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -9992,18 +10369,18 @@
         <v>226.08</v>
       </c>
       <c r="C3">
-        <v>223.89</v>
+        <v>221.32</v>
       </c>
       <c r="D3" s="21">
         <v>7.4999999999999997E-3</v>
       </c>
       <c r="E3" s="20">
-        <f>(B3-C3)</f>
-        <v>2.1900000000000261</v>
+        <f t="shared" si="0"/>
+        <v>4.7600000000000193</v>
       </c>
       <c r="F3" s="22">
-        <f>ROUNDUP(E3/(B3/100),2)</f>
-        <v>0.97</v>
+        <f t="shared" si="1"/>
+        <v>2.11</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -10014,18 +10391,18 @@
         <v>20.28</v>
       </c>
       <c r="C4" s="23">
-        <v>18.97</v>
+        <v>18.489999999999998</v>
       </c>
       <c r="D4" s="24">
         <v>3.0000000000000001E-3</v>
       </c>
       <c r="E4" s="25">
-        <f>(B4-C4)</f>
-        <v>1.3100000000000023</v>
+        <f t="shared" si="0"/>
+        <v>1.7900000000000027</v>
       </c>
       <c r="F4" s="26">
-        <f>ROUNDUP(E4/(B4/100),2)</f>
-        <v>6.46</v>
+        <f t="shared" si="1"/>
+        <v>8.83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -10036,18 +10413,18 @@
         <v>18.09</v>
       </c>
       <c r="C5">
-        <v>19.71</v>
+        <v>19.920000000000002</v>
       </c>
       <c r="D5" s="21">
         <v>9.1999999999999998E-3</v>
       </c>
       <c r="E5" s="20">
-        <f>(B5-C5)</f>
-        <v>-1.620000000000001</v>
+        <f t="shared" si="0"/>
+        <v>-1.8300000000000018</v>
       </c>
       <c r="F5" s="22">
-        <f>ROUNDUP(E5/(B5/100),2)</f>
-        <v>-8.9599999999999991</v>
+        <f t="shared" si="1"/>
+        <v>-10.119999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -10058,18 +10435,18 @@
         <v>36.08</v>
       </c>
       <c r="C6">
-        <v>35.01</v>
+        <v>34.81</v>
       </c>
       <c r="D6" s="21">
         <v>9.7999999999999997E-3</v>
       </c>
       <c r="E6" s="20">
-        <f>(B6-C6)</f>
-        <v>1.0700000000000003</v>
+        <f t="shared" si="0"/>
+        <v>1.269999999999996</v>
       </c>
       <c r="F6" s="22">
-        <f>ROUNDUP(E6/(B6/100),2)</f>
-        <v>2.9699999999999998</v>
+        <f t="shared" si="1"/>
+        <v>3.5199999999999996</v>
       </c>
     </row>
     <row r="7" spans="1:7" s="22" customFormat="1" x14ac:dyDescent="0.25">
@@ -10080,18 +10457,18 @@
         <v>128.4</v>
       </c>
       <c r="C7" s="20">
-        <v>119.11</v>
+        <v>116.43</v>
       </c>
       <c r="D7" s="21">
         <v>8.5000000000000006E-3</v>
       </c>
       <c r="E7" s="20">
-        <f>(B7-C7)</f>
-        <v>9.2900000000000063</v>
+        <f t="shared" si="0"/>
+        <v>11.969999999999999</v>
       </c>
       <c r="F7" s="22">
-        <f>ROUNDUP(E7/(B7/100),2)</f>
-        <v>7.24</v>
+        <f t="shared" si="1"/>
+        <v>9.33</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -10102,18 +10479,18 @@
         <v>910.66</v>
       </c>
       <c r="C8">
-        <v>897.34</v>
+        <v>883.85</v>
       </c>
       <c r="D8" s="21">
         <v>6.7000000000000002E-3</v>
       </c>
       <c r="E8" s="20">
-        <f t="shared" ref="E8:E42" si="0">(B8-C8)</f>
-        <v>13.319999999999936</v>
+        <f t="shared" ref="E8:E42" si="2">(B8-C8)</f>
+        <v>26.809999999999945</v>
       </c>
       <c r="F8" s="22">
-        <f t="shared" ref="F8:F42" si="1">ROUNDUP(E8/(B8/100),2)</f>
-        <v>1.47</v>
+        <f t="shared" ref="F8:F42" si="3">ROUNDUP(E8/(B8/100),2)</f>
+        <v>2.9499999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -10124,18 +10501,18 @@
         <v>20.41</v>
       </c>
       <c r="C9">
-        <v>23.55</v>
+        <v>25.18</v>
       </c>
       <c r="D9" s="21">
         <v>6.1000000000000004E-3</v>
       </c>
       <c r="E9" s="20">
-        <f t="shared" si="0"/>
-        <v>-3.1400000000000006</v>
+        <f t="shared" si="2"/>
+        <v>-4.7699999999999996</v>
       </c>
       <c r="F9" s="22">
-        <f t="shared" si="1"/>
-        <v>-15.39</v>
+        <f t="shared" si="3"/>
+        <v>-23.380000000000003</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -10146,16 +10523,16 @@
         <v>44.37</v>
       </c>
       <c r="C10" s="23">
-        <v>45.01</v>
+        <v>44.93</v>
       </c>
       <c r="D10" s="27"/>
       <c r="E10" s="20">
         <f>(B10-C10)</f>
-        <v>-0.64000000000000057</v>
+        <v>-0.56000000000000227</v>
       </c>
       <c r="F10" s="22">
         <f>ROUNDUP(E10/(B10/100),2)</f>
-        <v>-1.45</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="11" spans="1:7" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -10166,16 +10543,16 @@
         <v>19.25</v>
       </c>
       <c r="C11" s="23">
-        <v>17.53</v>
+        <v>17.260000000000002</v>
       </c>
       <c r="D11" s="24"/>
       <c r="E11" s="25">
         <f>(B11-C11)</f>
-        <v>1.7199999999999989</v>
+        <v>1.9899999999999984</v>
       </c>
       <c r="F11" s="26">
         <f>ROUNDUP(E11/(B11/100),2)</f>
-        <v>8.94</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -10186,16 +10563,16 @@
         <v>407.44</v>
       </c>
       <c r="C12" s="23">
-        <v>422.52</v>
+        <v>418.22</v>
       </c>
       <c r="D12" s="27"/>
       <c r="E12" s="20">
         <f>(B12-C12)</f>
-        <v>-15.079999999999984</v>
+        <v>-10.78000000000003</v>
       </c>
       <c r="F12" s="26">
         <f>ROUNDUP(E12/(B12/100),2)</f>
-        <v>-3.71</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -10206,16 +10583,16 @@
         <v>51.04</v>
       </c>
       <c r="C13" s="23">
-        <v>49.04</v>
+        <v>47.73</v>
       </c>
       <c r="D13" s="27"/>
       <c r="E13" s="20">
         <f>(B13-C13)</f>
-        <v>2</v>
+        <v>3.3100000000000023</v>
       </c>
       <c r="F13" s="22">
         <f>ROUNDUP(E13/(B13/100),2)</f>
-        <v>3.92</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -10226,16 +10603,16 @@
         <v>402.46</v>
       </c>
       <c r="C14" s="23">
-        <v>337.14</v>
+        <v>319.94</v>
       </c>
       <c r="D14" s="27"/>
       <c r="E14" s="20">
         <f>(B14-C14)</f>
-        <v>65.319999999999993</v>
+        <v>82.519999999999982</v>
       </c>
       <c r="F14" s="26">
         <f>ROUNDUP(E14/(B14/100),2)</f>
-        <v>16.240000000000002</v>
+        <v>20.51</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -10256,16 +10633,16 @@
         <v>9.92</v>
       </c>
       <c r="C16">
-        <v>9.6</v>
+        <v>9.41</v>
       </c>
       <c r="D16" s="21"/>
       <c r="E16" s="20">
-        <f t="shared" si="0"/>
-        <v>0.32000000000000028</v>
+        <f t="shared" si="2"/>
+        <v>0.50999999999999979</v>
       </c>
       <c r="F16" s="22">
-        <f t="shared" si="1"/>
-        <v>3.23</v>
+        <f t="shared" si="3"/>
+        <v>5.1499999999999995</v>
       </c>
     </row>
     <row r="17" spans="1:6" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -10276,18 +10653,18 @@
         <v>243.78</v>
       </c>
       <c r="C17" s="23">
-        <v>224.62</v>
+        <v>219.11</v>
       </c>
       <c r="D17" s="24">
         <v>1.9E-3</v>
       </c>
       <c r="E17" s="25">
-        <f t="shared" si="0"/>
-        <v>19.159999999999997</v>
+        <f t="shared" si="2"/>
+        <v>24.669999999999987</v>
       </c>
       <c r="F17" s="19">
-        <f t="shared" si="1"/>
-        <v>7.8599999999999994</v>
+        <f t="shared" si="3"/>
+        <v>10.119999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:6" s="23" customFormat="1" x14ac:dyDescent="0.25">
@@ -10298,18 +10675,18 @@
         <v>10.84</v>
       </c>
       <c r="C18" s="23">
-        <v>8.68</v>
+        <v>8.33</v>
       </c>
       <c r="D18" s="24">
         <v>4.7000000000000002E-3</v>
       </c>
       <c r="E18" s="25">
-        <f t="shared" si="0"/>
-        <v>2.16</v>
+        <f t="shared" si="2"/>
+        <v>2.5099999999999998</v>
       </c>
       <c r="F18" s="19">
-        <f t="shared" si="1"/>
-        <v>19.930000000000003</v>
+        <f t="shared" si="3"/>
+        <v>23.16</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -10328,11 +10705,11 @@
         <v>138.91999999999999</v>
       </c>
       <c r="E26" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>48.080000000000013</v>
       </c>
       <c r="F26" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>25.720000000000002</v>
       </c>
     </row>
@@ -10347,11 +10724,11 @@
         <v>139.94</v>
       </c>
       <c r="E27" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>40.06</v>
       </c>
       <c r="F27" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>22.26</v>
       </c>
     </row>
@@ -10366,11 +10743,11 @@
         <v>138.75</v>
       </c>
       <c r="E28" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>41.25</v>
       </c>
       <c r="F28" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>22.92</v>
       </c>
     </row>
@@ -10385,11 +10762,11 @@
         <v>142.24</v>
       </c>
       <c r="E29" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>52.56</v>
       </c>
       <c r="F29" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>26.990000000000002</v>
       </c>
     </row>
@@ -10411,11 +10788,11 @@
         <v>132.41999999999999</v>
       </c>
       <c r="E31" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>6.5800000000000125</v>
       </c>
       <c r="F31" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.74</v>
       </c>
     </row>
@@ -10430,11 +10807,11 @@
         <v>127.42</v>
       </c>
       <c r="E32" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>8.480000000000004</v>
       </c>
       <c r="F32" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>6.24</v>
       </c>
     </row>
@@ -10449,11 +10826,11 @@
         <v>131.51</v>
       </c>
       <c r="E33" s="29">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10.710000000000008</v>
       </c>
       <c r="F33" s="28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7.54</v>
       </c>
     </row>
@@ -10468,11 +10845,11 @@
         <v>10194.200000000001</v>
       </c>
       <c r="E34" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1282.7999999999993</v>
       </c>
       <c r="F34" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>11.18</v>
       </c>
     </row>
@@ -10487,11 +10864,11 @@
         <v>91.29</v>
       </c>
       <c r="E35" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.7099999999999937</v>
       </c>
       <c r="F35" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.84</v>
       </c>
     </row>
@@ -10506,11 +10883,11 @@
         <v>108.05</v>
       </c>
       <c r="E36" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1.8500000000000085</v>
       </c>
       <c r="F36" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.69</v>
       </c>
     </row>
@@ -10525,11 +10902,11 @@
         <v>94.19</v>
       </c>
       <c r="E37" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.769999999999996</v>
       </c>
       <c r="F37" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>2.86</v>
       </c>
     </row>
@@ -10544,11 +10921,11 @@
         <v>17.329999999999998</v>
       </c>
       <c r="E38" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.59000000000000341</v>
       </c>
       <c r="F38" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.3</v>
       </c>
     </row>
@@ -10570,11 +10947,11 @@
         <v>0.1</v>
       </c>
       <c r="E40" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10</v>
       </c>
       <c r="F40" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>12.26</v>
       </c>
     </row>
@@ -10589,11 +10966,11 @@
         <v>738.76</v>
       </c>
       <c r="E41" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>86.840000000000032</v>
       </c>
       <c r="F41" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>10.52</v>
       </c>
     </row>
@@ -10608,11 +10985,11 @@
         <v>172.88</v>
       </c>
       <c r="E42" s="25">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>17.069999999999993</v>
       </c>
       <c r="F42" s="19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>8.99</v>
       </c>
     </row>

--- a/Holdings09feb2026.xlsx
+++ b/Holdings09feb2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investment\pms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2B4786-C549-4518-B601-F583EBFE6E96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BF9E55-FA77-4E33-AA42-8A4D9C0F8777}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="9" xr2:uid="{A59C9408-6FFB-4B1A-950F-E0ADD8156D3D}"/>
   </bookViews>
@@ -28,6 +28,17 @@
     <sheet name="Sheet2" sheetId="17" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -2148,7 +2159,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2246,13 +2257,6 @@
     <xf numFmtId="0" fontId="16" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="29" fillId="33" borderId="0" xfId="42" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="29" fillId="33" borderId="0" xfId="42" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="42"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="42" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="42" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -7156,13 +7160,13 @@
       <c r="A82" t="s">
         <v>441</v>
       </c>
-      <c r="C82" s="60">
+      <c r="C82" s="57">
         <v>46125</v>
       </c>
-      <c r="D82" s="59">
+      <c r="D82" s="35">
         <v>300</v>
       </c>
-      <c r="F82" s="59">
+      <c r="F82" s="35">
         <v>105</v>
       </c>
       <c r="G82" s="37" t="s">
@@ -7257,22 +7261,22 @@
       <c r="Q85" s="47"/>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A86" s="57" t="s">
+      <c r="A86" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="B86" s="57" t="s">
+      <c r="B86" s="34" t="s">
         <v>431</v>
       </c>
-      <c r="C86" s="57" t="s">
+      <c r="C86" s="34" t="s">
         <v>432</v>
       </c>
-      <c r="D86" s="58">
+      <c r="D86" s="35">
         <v>20</v>
       </c>
-      <c r="E86" s="58">
+      <c r="E86" s="35">
         <v>1</v>
       </c>
-      <c r="F86" s="58">
+      <c r="F86" s="35">
         <v>20</v>
       </c>
     </row>
@@ -7317,22 +7321,22 @@
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A89" s="57" t="s">
+      <c r="A89" s="34" t="s">
         <v>421</v>
       </c>
-      <c r="B89" s="57" t="s">
+      <c r="B89" s="34" t="s">
         <v>248</v>
       </c>
-      <c r="C89" s="57" t="s">
+      <c r="C89" s="34" t="s">
         <v>435</v>
       </c>
-      <c r="D89" s="58">
+      <c r="D89" s="35">
         <v>400</v>
       </c>
-      <c r="E89" s="58">
+      <c r="E89" s="35">
         <v>8</v>
       </c>
-      <c r="F89" s="58">
+      <c r="F89" s="35">
         <v>3200</v>
       </c>
     </row>
@@ -7356,43 +7360,43 @@
         <v>750</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A91" s="57" t="s">
+    <row r="91" spans="1:17" s="49" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="46" t="s">
         <v>152</v>
       </c>
-      <c r="B91" s="57" t="s">
+      <c r="B91" s="46" t="s">
         <v>437</v>
       </c>
-      <c r="C91" s="57" t="s">
+      <c r="C91" s="46" t="s">
         <v>438</v>
       </c>
-      <c r="D91" s="58">
+      <c r="D91" s="47">
         <v>5</v>
       </c>
-      <c r="E91" s="58">
+      <c r="E91" s="47">
         <v>11</v>
       </c>
-      <c r="F91" s="58">
+      <c r="F91" s="47">
         <v>55</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A92" s="57" t="s">
+    <row r="92" spans="1:17" s="49" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="B92" s="57" t="s">
+      <c r="B92" s="46" t="s">
         <v>287</v>
       </c>
-      <c r="C92" s="57" t="s">
+      <c r="C92" s="46" t="s">
         <v>438</v>
       </c>
-      <c r="D92" s="58">
+      <c r="D92" s="47">
         <v>60</v>
       </c>
-      <c r="E92" s="58">
+      <c r="E92" s="47">
         <v>4</v>
       </c>
-      <c r="F92" s="58">
+      <c r="F92" s="47">
         <v>240</v>
       </c>
     </row>
@@ -7417,102 +7421,102 @@
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A94" s="57" t="s">
+      <c r="A94" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B94" s="57" t="s">
+      <c r="B94" s="34" t="s">
         <v>289</v>
       </c>
-      <c r="C94" s="57" t="s">
+      <c r="C94" s="34" t="s">
         <v>439</v>
       </c>
-      <c r="D94" s="58">
+      <c r="D94" s="35">
         <v>110</v>
       </c>
-      <c r="E94" s="58">
+      <c r="E94" s="35">
         <v>2.1</v>
       </c>
-      <c r="F94" s="58">
+      <c r="F94" s="35">
         <v>231</v>
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A95" s="57" t="s">
+      <c r="A95" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="B95" s="57" t="s">
+      <c r="B95" s="34" t="s">
         <v>184</v>
       </c>
-      <c r="C95" s="57" t="s">
+      <c r="C95" s="34" t="s">
         <v>439</v>
       </c>
-      <c r="D95" s="58">
+      <c r="D95" s="35">
         <v>30</v>
       </c>
-      <c r="E95" s="58">
+      <c r="E95" s="35">
         <v>13</v>
       </c>
-      <c r="F95" s="58">
+      <c r="F95" s="35">
         <v>390</v>
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A96" s="57" t="s">
+      <c r="A96" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B96" s="57" t="s">
+      <c r="B96" s="34" t="s">
         <v>272</v>
       </c>
-      <c r="C96" s="57" t="s">
+      <c r="C96" s="34" t="s">
         <v>440</v>
       </c>
-      <c r="D96" s="58">
+      <c r="D96" s="35">
         <v>20</v>
       </c>
-      <c r="E96" s="58">
+      <c r="E96" s="35">
         <v>23</v>
       </c>
-      <c r="F96" s="58">
+      <c r="F96" s="35">
         <v>460</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="57" t="s">
+      <c r="A97" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="B97" s="57" t="s">
+      <c r="B97" s="34" t="s">
         <v>288</v>
       </c>
-      <c r="C97" s="57" t="s">
+      <c r="C97" s="34" t="s">
         <v>440</v>
       </c>
-      <c r="D97" s="58">
+      <c r="D97" s="35">
         <v>125</v>
       </c>
-      <c r="E97" s="58">
+      <c r="E97" s="35">
         <v>2.5</v>
       </c>
-      <c r="F97" s="58">
+      <c r="F97" s="35">
         <v>312.5</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A98" s="57" t="s">
+    <row r="98" spans="1:6" s="49" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="46" t="s">
         <v>290</v>
       </c>
-      <c r="B98" s="57" t="s">
+      <c r="B98" s="46" t="s">
         <v>189</v>
       </c>
-      <c r="C98" s="57" t="s">
+      <c r="C98" s="46" t="s">
         <v>440</v>
       </c>
-      <c r="D98" s="58">
+      <c r="D98" s="47">
         <v>90</v>
       </c>
-      <c r="E98" s="58">
+      <c r="E98" s="47">
         <v>22</v>
       </c>
-      <c r="F98" s="58">
+      <c r="F98" s="47">
         <v>1980</v>
       </c>
     </row>
